--- a/Electricty_051326.xlsx
+++ b/Electricty_051326.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cwp.sharepoint.com/projects/Documents/T-22-011/Task 2. Toolkit and Training Content/Calculators to Evaluate Progress/ForGitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7877175B-2028-48E1-971E-154C21E46C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{7877175B-2028-48E1-971E-154C21E46C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1142CE96-92B5-4DE1-8BFF-919BD0952B15}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1695" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FE24DBEA-2498-4AE1-8BA4-A8610A04BD03}"/>
+    <workbookView xWindow="28680" yWindow="1695" windowWidth="29040" windowHeight="15720" xr2:uid="{FE24DBEA-2498-4AE1-8BA4-A8610A04BD03}"/>
   </bookViews>
   <sheets>
     <sheet name="eGrid2023" sheetId="2" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="43">
   <si>
     <t>Table 8.4 Puerto Rico- Average Price of Electricity to Ultimate Customers:</t>
   </si>
@@ -165,6 +165,21 @@
   </si>
   <si>
     <t>Puerto Rico</t>
+  </si>
+  <si>
+    <t>NYC/Westchester, NY</t>
+  </si>
+  <si>
+    <t>Long Island, NY</t>
+  </si>
+  <si>
+    <t>Upstate New York</t>
+  </si>
+  <si>
+    <t>Puerto Rico and Virgin Islands</t>
+  </si>
+  <si>
+    <t>Name In Dropdown Menu</t>
   </si>
 </sst>
 </file>
@@ -948,23 +963,11 @@
     <xf numFmtId="4" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="37" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="19" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -981,7 +984,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="23" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1007,6 +1010,18 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1383,129 +1398,149 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{689DD985-0A03-46EC-A6E0-97DF0DA057C4}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="4" width="24.28515625" customWidth="1"/>
-    <col min="5" max="5" width="29.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="5" width="24.28515625" customWidth="1"/>
+    <col min="6" max="6" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="9" customFormat="1" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:6" s="7" customFormat="1" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="E1" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="24"/>
+      <c r="D2" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="27"/>
+      <c r="F2" s="25" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="16">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="12">
         <v>2023</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="E3" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="22">
+      <c r="F3" s="18">
         <v>977.96799999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="18">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="14">
         <v>2023</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="E4" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="23">
+      <c r="F4" s="19">
         <v>1319.396</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="18">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="14">
         <v>2023</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="E5" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="23">
+      <c r="F5" s="19">
         <v>911.78599999999994</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="18">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="14">
         <v>2023</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="E6" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="23">
+      <c r="F6" s="19">
         <v>1642.029</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20">
+    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="16">
         <v>2023</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="E7" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="24">
+      <c r="F7" s="20">
         <v>1180.4849999999999</v>
       </c>
     </row>
@@ -1528,24 +1563,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
     </row>
     <row r="2" spans="1:6" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -1568,14 +1603,14 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -1620,162 +1655,162 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="10" t="s">
+      <c r="C3" s="31"/>
+      <c r="D3" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="10" t="s">
+      <c r="E3" s="31"/>
+      <c r="F3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="10" t="s">
+      <c r="G3" s="31"/>
+      <c r="H3" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="10" t="s">
+      <c r="I3" s="31"/>
+      <c r="J3" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="11"/>
+      <c r="K3" s="31"/>
     </row>
     <row r="4" spans="1:11" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="10">
         <v>23.12</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="10">
         <v>19.690000000000001</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="10">
         <v>17.36</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="10">
         <v>15.23</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="10">
         <v>15.9</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="10">
         <v>13.48</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="10">
         <v>13.35</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="10">
         <v>11.82</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="10">
         <v>19.64</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="10">
         <v>16.88</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="10">
         <v>29.17</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="10">
         <v>25.76</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="10">
         <v>22.88</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="10">
         <v>20.62</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="10">
         <v>11.94</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="10">
         <v>11.22</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="10">
         <v>20.45</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="10">
         <v>14.54</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="10">
         <v>24.26</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="10">
         <v>21.45</v>
       </c>
     </row>
@@ -1794,6 +1829,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Date_x002f_Time xmlns="b031f331-093e-4af9-b9a8-5fb9941cd8bc" xsi:nil="true"/>
+    <Project xmlns="80727368-2d85-4693-8aca-8c33fb2339f5" xsi:nil="true"/>
+    <IconOverlay xmlns="http://schemas.microsoft.com/sharepoint/v4" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b031f331-093e-4af9-b9a8-5fb9941cd8bc">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SourceFile xmlns="b031f331-093e-4af9-b9a8-5fb9941cd8bc" xsi:nil="true"/>
+    <TaxCatchAll xmlns="61ea441e-408f-4c04-8adb-e628fdc370c0" xsi:nil="true"/>
+    <Notes xmlns="b031f331-093e-4af9-b9a8-5fb9941cd8bc" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Project Document" ma:contentTypeID="0x01010084099C5946FA6344AFBC08FDA28BB5E3000F2A5536EED47B428001DEFDF00DB8CF" ma:contentTypeVersion="31" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="8f6676a41b6ceaec622f6036fe6c719c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="80727368-2d85-4693-8aca-8c33fb2339f5" xmlns:ns3="http://schemas.microsoft.com/sharepoint/v4" xmlns:ns4="b031f331-093e-4af9-b9a8-5fb9941cd8bc" xmlns:ns5="61ea441e-408f-4c04-8adb-e628fdc370c0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f4c24d879343d354472f72dafe6cecf9" ns2:_="" ns3:_="" ns4:_="" ns5:_="">
     <xsd:import namespace="80727368-2d85-4693-8aca-8c33fb2339f5"/>
@@ -2124,39 +2184,44 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Date_x002f_Time xmlns="b031f331-093e-4af9-b9a8-5fb9941cd8bc" xsi:nil="true"/>
-    <Project xmlns="80727368-2d85-4693-8aca-8c33fb2339f5" xsi:nil="true"/>
-    <IconOverlay xmlns="http://schemas.microsoft.com/sharepoint/v4" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b031f331-093e-4af9-b9a8-5fb9941cd8bc">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SourceFile xmlns="b031f331-093e-4af9-b9a8-5fb9941cd8bc" xsi:nil="true"/>
-    <TaxCatchAll xmlns="61ea441e-408f-4c04-8adb-e628fdc370c0" xsi:nil="true"/>
-    <Notes xmlns="b031f331-093e-4af9-b9a8-5fb9941cd8bc" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB99A8C7-6F82-44F7-87E9-1ABCD041A7C2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2378BB5-632D-45AB-B418-9CDD9C268312}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b031f331-093e-4af9-b9a8-5fb9941cd8bc"/>
+    <ds:schemaRef ds:uri="80727368-2d85-4693-8aca-8c33fb2339f5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v4"/>
+    <ds:schemaRef ds:uri="61ea441e-408f-4c04-8adb-e628fdc370c0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01F7E911-371E-43A9-B231-4C373FC5E279}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01F7E911-371E-43A9-B231-4C373FC5E279}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2378BB5-632D-45AB-B418-9CDD9C268312}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB99A8C7-6F82-44F7-87E9-1ABCD041A7C2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="80727368-2d85-4693-8aca-8c33fb2339f5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v4"/>
+    <ds:schemaRef ds:uri="b031f331-093e-4af9-b9a8-5fb9941cd8bc"/>
+    <ds:schemaRef ds:uri="61ea441e-408f-4c04-8adb-e628fdc370c0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>